--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487537_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487537_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7502</v>
+        <v>4.363</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1418</v>
+        <v>5.3729</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3916</v>
+        <v>-1.0098</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1946</v>
+        <v>1.6107</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8965</v>
+        <v>-1.1216</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7019</v>
+        <v>2.7323</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7007</v>
+        <v>4.9565</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7308</v>
+        <v>0.2346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.97</v>
+        <v>4.7219</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.5061</v>
+        <v>-3.3458</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8342</v>
+        <v>-1.3562</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6718</v>
+        <v>-1.9896</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.5253</v>
+        <v>0.5875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>6.1396</v>
+        <v>1.7743</v>
       </c>
       <c r="T2" t="n">
-        <v>6.1207</v>
+        <v>1.3956</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0189</v>
+        <v>0.3786</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9412</v>
+        <v>0.3905</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2754</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2708</v>
+        <v>0.4314</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5212</v>
+        <v>3.6359</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2504</v>
+        <v>-3.2045</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6107</v>
+        <v>0.1946</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1216</v>
+        <v>1.8965</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7323</v>
+        <v>-1.7019</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9565</v>
+        <v>4.7007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2346</v>
+        <v>3.7308</v>
       </c>
       <c r="L3" t="n">
-        <v>4.7219</v>
+        <v>0.97</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3458</v>
+        <v>-4.5061</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3562</v>
+        <v>-1.8342</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9896</v>
+        <v>-2.6718</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5875</v>
+        <v>-3.5253</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-4.8962</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6821</v>
+        <v>2.8208</v>
       </c>
       <c r="T3" t="n">
-        <v>0.544</v>
+        <v>2.6148</v>
       </c>
       <c r="U3" t="n">
-        <v>0.138</v>
+        <v>0.206</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3905</v>
+        <v>0.9412</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3905</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6853</v>
+        <v>-0.3298</v>
       </c>
       <c r="E4" t="n">
-        <v>1.664</v>
+        <v>-0.4289</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9787</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.5564</v>
+        <v>-0.0833</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.0866</v>
+        <v>-0.1289</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4698</v>
+        <v>0.0456</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7502</v>
+        <v>0.3875</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1388</v>
+        <v>0.3471</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3886</v>
+        <v>0.0404</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8062</v>
+        <v>-0.4708</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9479</v>
+        <v>-0.476</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8584</v>
+        <v>0.0052</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7626</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8684</v>
+        <v>0.3411</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5282</v>
+        <v>0.1629</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3402</v>
+        <v>0.1782</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3894</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.114</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7008</v>
+        <v>-0.6227</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6929</v>
+        <v>0.4095</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0078</v>
+        <v>-1.0322</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0833</v>
+        <v>-3.5564</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1289</v>
+        <v>-3.0866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0456</v>
+        <v>-0.4698</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3875</v>
+        <v>-0.7502</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3471</v>
+        <v>-2.1388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0404</v>
+        <v>1.3886</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4708</v>
+        <v>-2.8062</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.476</v>
+        <v>-0.9479</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0052</v>
+        <v>-1.8584</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0299</v>
+        <v>2.5604</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1012</v>
+        <v>2.2737</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0713</v>
+        <v>0.2867</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.3894</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.114</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.539</v>
+        <v>-1.1203</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6442</v>
+        <v>-0.5591</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8948</v>
+        <v>-0.5612</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7409</v>
+        <v>-0.6237</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5233</v>
+        <v>-0.6189</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2176</v>
+        <v>-0.0048</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6618000000000001</v>
+        <v>1.0512</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0204</v>
+        <v>0.3998</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6822</v>
+        <v>0.6515</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0791</v>
+        <v>-1.675</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5437</v>
+        <v>-1.0187</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5354</v>
+        <v>-0.6563</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>-3.5253</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0061</v>
+        <v>1.2614</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0176</v>
+        <v>0.5393</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0115</v>
+        <v>0.7221</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8707</v>
+        <v>-1.2854</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4966</v>
+        <v>-0.3372</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3741</v>
+        <v>-0.9483</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6237</v>
+        <v>-1.7409</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6189</v>
+        <v>-0.5233</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0048</v>
+        <v>-1.2176</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0512</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3998</v>
+        <v>0.0204</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6515</v>
+        <v>-0.6822</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.675</v>
+        <v>-1.0791</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0187</v>
+        <v>-0.5437</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6563</v>
+        <v>-0.5354</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.5253</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>0.511</v>
+        <v>0.2597</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3982</v>
+        <v>0.3246</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9092</v>
+        <v>-0.065</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.145</v>
+        <v>-1.403</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3419</v>
+        <v>-1.8137</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1969</v>
+        <v>0.4108</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0695</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2967</v>
+        <v>1.0386</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2841</v>
+        <v>0.8122</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0126</v>
+        <v>0.2264</v>
       </c>
       <c r="V8" t="n">
         <v>0.9988</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4855</v>
+        <v>-2.8036</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4232</v>
+        <v>1.3924</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0623</v>
+        <v>-4.1959</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4242</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0232</v>
+        <v>1.6587</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6422</v>
+        <v>1.1733</v>
       </c>
       <c r="U9" t="n">
-        <v>0.619</v>
+        <v>0.4854</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.553</v>
+        <v>-3.6293</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4808</v>
+        <v>-2.2363</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0722</v>
+        <v>-1.393</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8948</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0292</v>
+        <v>0.8946</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4046</v>
+        <v>0.8399</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3755</v>
+        <v>0.0547</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.587699999999999</v>
+        <v>-6.3997</v>
       </c>
       <c r="E11" t="n">
-        <v>4.247400000000001</v>
+        <v>5.435499999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-11.835</v>
@@ -1312,13 +1312,13 @@
         <v>8.813000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>11.4216</v>
+        <v>12.6096</v>
       </c>
       <c r="T11" t="n">
-        <v>8.948399999999999</v>
+        <v>10.1363</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4732</v>
+        <v>2.4731</v>
       </c>
       <c r="V11" t="n">
         <v>2.433000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.7013</v>
+        <v>5.3097</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2533</v>
+        <v>5.0486</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.552</v>
+        <v>0.2611</v>
       </c>
       <c r="G12" t="n">
         <v>5.1111</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.525</v>
+        <v>-0.9166</v>
       </c>
       <c r="T12" t="n">
-        <v>0.414</v>
+        <v>0.2094</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9391</v>
+        <v>-1.126</v>
       </c>
       <c r="V12" t="n">
         <v>0.7235</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. TOMIC</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8234</v>
+        <v>3.5683</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0358</v>
+        <v>2.999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7876</v>
+        <v>0.5693</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2391</v>
+        <v>4.1634</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6404</v>
+        <v>3.2739</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8795</v>
+        <v>0.8895</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8287</v>
+        <v>4.3323</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6414</v>
+        <v>2.7917</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4701</v>
+        <v>1.5406</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4104</v>
+        <v>-0.1688</v>
       </c>
       <c r="N13" t="n">
-        <v>0.001</v>
+        <v>0.4822</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4093</v>
+        <v>-0.6511</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2133</v>
+        <v>-1.1032</v>
       </c>
       <c r="T13" t="n">
-        <v>0.207</v>
+        <v>-0.3541</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0063</v>
+        <v>-0.7491</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>M. TOMIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3608</v>
+        <v>3.4896</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2036</v>
+        <v>1.7287</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1572</v>
+        <v>1.7609</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1634</v>
+        <v>2.2391</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2739</v>
+        <v>-0.6404</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8895</v>
+        <v>2.8795</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3323</v>
+        <v>1.8287</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7917</v>
+        <v>-0.6414</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5406</v>
+        <v>2.4701</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1688</v>
+        <v>0.4104</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4822</v>
+        <v>0.001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6511</v>
+        <v>0.4093</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3107</v>
+        <v>-0.1204</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1494</v>
+        <v>-0.1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1613</v>
+        <v>-0.0204</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8999</v>
+        <v>2.9749</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3135</v>
+        <v>4.0298</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4136</v>
+        <v>-1.055</v>
       </c>
       <c r="G15" t="n">
         <v>4.1407</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.242</v>
+        <v>-1.167</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2474</v>
+        <v>-0.5311</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9946</v>
+        <v>-0.6359</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3905</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3488</v>
+        <v>1.3755</v>
       </c>
       <c r="E16" t="n">
         <v>1.0153</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3335</v>
+        <v>0.3602</v>
       </c>
       <c r="G16" t="n">
         <v>0.981</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2198</v>
+        <v>-0.1931</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5782</v>
+        <v>0.586</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1489</v>
+        <v>0.8606</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5708</v>
+        <v>-0.2745</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9994</v>
+        <v>0.6962</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7994</v>
+        <v>-0.1261</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9354</v>
+        <v>1.567</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6744</v>
+        <v>1.4409</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.739</v>
+        <v>0.1261</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7354</v>
+        <v>-0.9969</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.675</v>
+        <v>-0.7447</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0604</v>
+        <v>-0.2521</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0648</v>
+        <v>-0.7894</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8587</v>
+        <v>-0.1823</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.6071</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6659</v>
+        <v>0.2178</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6659</v>
+        <v>1.4344</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2956</v>
+        <v>0.1393</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6559</v>
+        <v>0.3303</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3603</v>
+        <v>-0.1909</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6962</v>
+        <v>1.9994</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1261</v>
+        <v>-1.7994</v>
       </c>
       <c r="J18" t="n">
-        <v>1.567</v>
+        <v>1.9354</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4409</v>
+        <v>2.6744</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1261</v>
+        <v>-0.739</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9969</v>
+        <v>-1.7354</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7447</v>
+        <v>-0.675</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2521</v>
+        <v>-1.0604</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0799</v>
+        <v>-0.3741</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.387</v>
+        <v>0.04</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6929</v>
+        <v>-0.414</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2178</v>
+        <v>-0.6659</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4344</v>
+        <v>-0.6659</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3049</v>
+        <v>0.0141</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4185</v>
+        <v>0.5209</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7235</v>
+        <v>-0.5068</v>
       </c>
       <c r="G19" t="n">
         <v>0.9176</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7893</v>
+        <v>-0.4704</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4329</v>
+        <v>-0.2163</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SOTO MARTINEZ</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.523</v>
+        <v>-0.3358</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1188</v>
+        <v>0.8671</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4042</v>
+        <v>-1.2029</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4042</v>
+        <v>1.2053</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.3161</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4042</v>
+        <v>-0.1109</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.1928</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.3797</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.8131</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4042</v>
+        <v>-0.9875</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.0635</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4042</v>
+        <v>-0.924</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1188</v>
+        <v>-1.5411</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1188</v>
+        <v>-0.3464</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-1.1946</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>A. SOTO MARTINEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3222</v>
+        <v>-0.4206</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5601</v>
+        <v>-0.0165</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8824</v>
+        <v>-0.4042</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2053</v>
+        <v>-0.4042</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3161</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1109</v>
+        <v>-0.4042</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1928</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3797</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8131</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9875</v>
+        <v>-0.4042</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0635</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.924</v>
+        <v>-0.4042</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.5275</v>
+        <v>-0.0165</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6534</v>
+        <v>-0.0165</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8741</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7871</v>
+        <v>-2.4414</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4547</v>
+        <v>-2.3524</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3324</v>
+        <v>-0.089</v>
       </c>
       <c r="G22" t="n">
         <v>-3.125</v>
@@ -2170,13 +2170,13 @@
         <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5998</v>
+        <v>-0.2541</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3276</v>
+        <v>-0.2253</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2722</v>
+        <v>-0.0288</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2166</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4831</v>
+        <v>-3.2609</v>
       </c>
       <c r="E23" t="n">
         <v>-3.1963</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2868</v>
+        <v>-0.0645</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4116</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2869</v>
+        <v>-1.0647</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4752</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8117</v>
+        <v>-0.5895</v>
       </c>
       <c r="V23" t="n">
         <v>0.3905</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.587699999999998</v>
+        <v>10.9987</v>
       </c>
       <c r="E24" t="n">
         <v>11.8351</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2477</v>
+        <v>-0.8363</v>
       </c>
       <c r="G24" t="n">
         <v>14.5875</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8429</v>
+        <v>7.842900000000002</v>
       </c>
       <c r="I24" t="n">
         <v>6.7445</v>
@@ -2326,13 +2326,13 @@
         <v>15.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.4216</v>
+        <v>-8.0106</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4731</v>
+        <v>-2.4732</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.948600000000001</v>
+        <v>-5.537100000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4332</v>
